--- a/Session 7 - BST/DS Lab report sheet_2.xlsx
+++ b/Session 7 - BST/DS Lab report sheet_2.xlsx
@@ -1,25 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varin\Documents\Data Structure Git\Data-Structure-Library-1402\Session 7 - BST\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640EB753-4452-438E-A997-463927A3AF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Student Name</t>
   </si>
   <si>
     <t>Student ID</t>
-  </si>
-  <si>
-    <t>محمدرضا امینی</t>
   </si>
   <si>
     <t>Platform</t>
@@ -82,45 +88,54 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="9">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;Helvetica Neue&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;Helvetica Neue&quot;"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="&quot;Helvetica Neue&quot;"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
     <font>
       <i/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;Helvetica Neue&quot;"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -131,7 +146,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -141,67 +156,78 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -218,7 +244,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0">
+              <a:rPr lang="en-US" b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -231,15 +257,24 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Insert time</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -253,17 +288,59 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Sheet1!$A$12:$A$16</c:f>
-            </c:strRef>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Sheet1!$B$12:$B$16</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.33959460299999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.80041527700000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.4854805469999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.6235921379999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.9261178970336896</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-26C4-4E7F-B319-5E65D561CE7B}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -271,6 +348,12 @@
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$C$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Successful Search</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -284,17 +367,59 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Sheet1!$A$12:$A$16</c:f>
-            </c:strRef>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Sheet1!$C$12:$C$16</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>9.9987979999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9836187000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.4100990000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.9295635000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.120773553848266</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-26C4-4E7F-B319-5E65D561CE7B}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -302,6 +427,12 @@
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$D$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Unsuccessful Search</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -315,18 +446,69 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Sheet1!$A$12:$A$16</c:f>
-            </c:strRef>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Sheet1!$D$12:$D$16</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.301837E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7524003999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9701690999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.8490973000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.12425947189331001</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-26C4-4E7F-B319-5E65D561CE7B}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
         <c:axId val="173846438"/>
         <c:axId val="697114239"/>
       </c:lineChart>
@@ -352,7 +534,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0">
+                  <a:rPr lang="en-US" b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -368,7 +550,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:spPr/>
+        <c:tickLblPos val="nextTo"/>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
@@ -381,9 +563,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="697114239"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="697114239"/>
@@ -426,15 +614,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -459,9 +639,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="173846438"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -479,16 +662,24 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
@@ -497,9 +688,15 @@
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6753225" cy="3533775"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1" title="Chart"/>
+        <xdr:cNvPr id="2" name="Chart 1" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -508,7 +705,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -518,7 +715,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -708,24 +905,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z17"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.25"/>
-    <col customWidth="1" min="2" max="2" width="15.38"/>
-    <col customWidth="1" min="3" max="3" width="18.38"/>
-    <col customWidth="1" min="4" max="4" width="17.25"/>
-    <col customWidth="1" min="5" max="5" width="18.5"/>
+    <col min="1" max="1" width="14.21875" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -737,19 +937,15 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5">
-        <v>4.0222202E8</v>
-      </c>
+    <row r="2" spans="1:26">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -757,53 +953,53 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="D6" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E6" s="5">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F6" s="3"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -811,31 +1007,31 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26">
       <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26">
       <c r="A9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -843,135 +1039,135 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:26">
+      <c r="A11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="A12" s="4">
+        <v>100000</v>
+      </c>
+      <c r="B12" s="4">
+        <v>0.33959460299999999</v>
+      </c>
+      <c r="C12" s="4">
+        <v>9.9987979999999997E-3</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1.301837E-2</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10">
-        <v>100000.0</v>
-      </c>
-      <c r="B12" s="10">
-        <v>0.339594603</v>
-      </c>
-      <c r="C12" s="10">
-        <v>0.009998798</v>
-      </c>
-      <c r="D12" s="10">
-        <v>0.01301837</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>21</v>
-      </c>
       <c r="F12" s="2"/>
     </row>
-    <row r="13">
-      <c r="A13" s="10">
-        <v>200000.0</v>
-      </c>
-      <c r="B13" s="10">
-        <v>0.800415277</v>
-      </c>
-      <c r="C13" s="10">
-        <v>0.019836187</v>
-      </c>
-      <c r="D13" s="10">
-        <v>0.017524004</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>21</v>
+    <row r="13" spans="1:26">
+      <c r="A13" s="4">
+        <v>200000</v>
+      </c>
+      <c r="B13" s="4">
+        <v>0.80041527700000004</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1.9836187000000002E-2</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1.7524003999999999E-2</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="F13" s="2"/>
     </row>
-    <row r="14">
-      <c r="A14" s="10">
-        <v>500000.0</v>
-      </c>
-      <c r="B14" s="10">
-        <v>2.485480547</v>
-      </c>
-      <c r="C14" s="10">
-        <v>0.05410099</v>
-      </c>
-      <c r="D14" s="10">
-        <v>0.049701691</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>21</v>
+    <row r="14" spans="1:26">
+      <c r="A14" s="4">
+        <v>500000</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2.4854805469999999</v>
+      </c>
+      <c r="C14" s="4">
+        <v>5.4100990000000002E-2</v>
+      </c>
+      <c r="D14" s="4">
+        <v>4.9701690999999999E-2</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="F14" s="2"/>
     </row>
-    <row r="15">
-      <c r="A15" s="10">
-        <v>700000.0</v>
-      </c>
-      <c r="B15" s="10">
-        <v>3.623592138</v>
-      </c>
-      <c r="C15" s="10">
-        <v>0.079295635</v>
-      </c>
-      <c r="D15" s="10">
-        <v>0.078490973</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>21</v>
+    <row r="15" spans="1:26">
+      <c r="A15" s="4">
+        <v>700000</v>
+      </c>
+      <c r="B15" s="4">
+        <v>3.6235921379999998</v>
+      </c>
+      <c r="C15" s="4">
+        <v>7.9295635000000003E-2</v>
+      </c>
+      <c r="D15" s="4">
+        <v>7.8490973000000006E-2</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="F15" s="2"/>
     </row>
-    <row r="16">
-      <c r="A16" s="11">
-        <v>1000000.0</v>
-      </c>
-      <c r="B16" s="11">
-        <v>5.92611789703369</v>
-      </c>
-      <c r="C16" s="11">
+    <row r="16" spans="1:26">
+      <c r="A16" s="8">
+        <v>1000000</v>
+      </c>
+      <c r="B16" s="8">
+        <v>5.9261178970336896</v>
+      </c>
+      <c r="C16" s="8">
         <v>0.120773553848266</v>
       </c>
-      <c r="D16" s="11">
-        <v>0.12425947189331</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
-      <c r="U16" s="13"/>
-      <c r="V16" s="13"/>
-      <c r="W16" s="13"/>
-      <c r="X16" s="13"/>
-      <c r="Y16" s="13"/>
-      <c r="Z16" s="13"/>
-    </row>
-    <row r="17">
+      <c r="D16" s="8">
+        <v>0.12425947189331001</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="9"/>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -983,6 +1179,7 @@
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>